--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133729073</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133729073</v>
+        <v>133729080</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550431</v>
+        <v>550566</v>
       </c>
       <c r="R2" t="n">
-        <v>6998665</v>
+        <v>6998483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133729081</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>550566</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6998483</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133729073</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550431</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6998665</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133729080</v>
+        <v>134654417</v>
       </c>
       <c r="B2" t="n">
-        <v>80488</v>
+        <v>99101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550566</v>
+        <v>550432</v>
       </c>
       <c r="R2" t="n">
-        <v>6998483</v>
+        <v>6998792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133729081</v>
+        <v>134654419</v>
       </c>
       <c r="B3" t="n">
-        <v>80492</v>
+        <v>99101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550566</v>
+        <v>550425</v>
       </c>
       <c r="R3" t="n">
-        <v>6998483</v>
+        <v>6998795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,57 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133729073</v>
+        <v>134654421</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>99101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550431</v>
+        <v>550422</v>
       </c>
       <c r="R4" t="n">
-        <v>6998665</v>
+        <v>6998798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,15 +954,888 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134654422</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>504</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550413</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6998800</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133729080</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550566</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6998483</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133729081</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550566</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6998483</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134654423</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>550416</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6998821</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134654418</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>550425</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6998795</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134654415</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99533</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>550436</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6998740</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133729073</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granliden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550431</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6998665</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134654420</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550422</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6998798</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134654424</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99232</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>550426</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6998816</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20088-2023 artfynd.xlsx
+++ b/artfynd/A 20088-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654419</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654421</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654422</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729081</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654418</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654415</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729073</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654420</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,8 +1896,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>